--- a/docs/xlsx/jobs-2026-08-27.xlsx
+++ b/docs/xlsx/jobs-2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="655">
   <si>
     <t>Title</t>
   </si>
@@ -406,6 +406,186 @@
     <t>https://www.conservationjobboard.com/job-listing-workers-compensation-specialist-remote-remote/4671046176</t>
   </si>
   <si>
+    <t>Academic Tutor (Part-Time)</t>
+  </si>
+  <si>
+    <t>Aspire Education</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3534ccbbc8c34c248b1e8e45b98141ff-academic-tutor-part-time-aspire-education-san-francisco</t>
+  </si>
+  <si>
+    <t>Administrative &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>The Congregation of the Sisters of St. Joseph of Boston and The Sponsored Ministries</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26b04abf0a414285acb9d0185c77fce3-administrative-operations-coordinator-the-congregation-of-the-sisters-of-st-joseph-of-boston-and-the-sponsored-ministries-newton</t>
+  </si>
+  <si>
+    <t>Administrative and Member Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Florida Association of Free and Charitable Clinics</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/721e72aea29a4e20ae89f14a128856bc-administrative-and-member-engagement-coordinator-florida-association-of-free-and-charitable-clinics-jacksonville</t>
+  </si>
+  <si>
+    <t>Administrative Office Assistant</t>
+  </si>
+  <si>
+    <t>Symphonicity</t>
+  </si>
+  <si>
+    <t>Virginia Beach, Virginia</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6aee0b3e0204462c83f5c4c987c4b112-administrative-office-assistant-symphonicity-virginia-beach</t>
+  </si>
+  <si>
+    <t>Associate Director of Business Services</t>
+  </si>
+  <si>
+    <t>Center on Deafness</t>
+  </si>
+  <si>
+    <t>Northbrook, Illinois</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d77871826874456ba7444d4f88c59722-associate-director-of-business-services-center-on-deafness-northbrook</t>
+  </si>
+  <si>
+    <t>Associate Director of Development</t>
+  </si>
+  <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6661a4e8edae4c588678bd17103b5e68-associate-director-of-development-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>ASSOCIATE/SENIOR COUNSEL – VOTING RIGHTS</t>
+  </si>
+  <si>
+    <t>LatinoJustice PRLDEF</t>
+  </si>
+  <si>
+    <t>USD 90878.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cf21d409c0343fa88a37d3c3a3d5124-associatesenior-counsel-voting-rights-latinojustice-prldef-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual (English/Spanish) Immigration Program Specialist</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Urban Areas, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb3e55f7c2fa45968988bc7e04fa43b5-bilingual-englishspanish-immigration-program-specialist-masa-bronx</t>
+  </si>
+  <si>
+    <t>Bilingual (English/Spanish) Program Associate</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/465847bd926d471a86491d28fd076c76-bilingual-englishspanish-program-associate-masa-bronx</t>
+  </si>
+  <si>
+    <t>Bilingual Community Engagement/Participación Comunitaria Lead</t>
+  </si>
+  <si>
+    <t>LandPaths</t>
+  </si>
+  <si>
+    <t>Santa Rosa, California</t>
+  </si>
+  <si>
+    <t>USD 31.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04c80cd426d14577aae0d27e9a638eb8-bilingual-community-engagementparticipacion-comunitaria-lead-landpaths-santa-rosa</t>
+  </si>
+  <si>
     <t>Business Operations Associate</t>
   </si>
   <si>
@@ -415,9 +595,6 @@
     <t>Remote</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -427,6 +604,348 @@
     <t>https://www.idealist.org/en/consultant-job/2ae64e728522479b99208b345209c277-business-operations-associate-ilo-group-matthews</t>
   </si>
   <si>
+    <t>California Finance Director</t>
+  </si>
+  <si>
+    <t>Working Families</t>
+  </si>
+  <si>
+    <t>USD 64900.00 - 91800.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf77740d6d3840139bf4f1cce0acd946-california-finance-director-working-families-kings-county</t>
+  </si>
+  <si>
+    <t>Canvasser, Civic Engagement</t>
+  </si>
+  <si>
+    <t>Hispanic Federation</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/222c15d8965649bfbcc326370bacffec-canvasser-civic-engagement-hispanic-federation-orlando</t>
+  </si>
+  <si>
+    <t>CASE MANAGER – FAMILY PRESERVATION PROJECT</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 53140.00 - 84340.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/587269f67f914a7b8e53866ea0a2d93a-case-manager-family-preservation-project-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>James House</t>
+  </si>
+  <si>
+    <t>Prince George, Virginia</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 99000.00/year</t>
+  </si>
+  <si>
+    <t>Victim Support, Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4629f9db36454681a5e8d80c11f19915-chief-executive-officer-james-house-prince-george</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer, Ijams Nature Center</t>
+  </si>
+  <si>
+    <t>Potrero Group</t>
+  </si>
+  <si>
+    <t>Knoxville, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3c1622ce7dbb4485a493f79141acd7fe-chief-executive-officer-ijams-nature-center-potrero-group-knoxville</t>
+  </si>
+  <si>
+    <t>Clinical Trial Manager, Lupus Therapeutics</t>
+  </si>
+  <si>
+    <t>Lupus Research Alliance</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/437f35201a6c4272aefe36890a3ae292-clinical-trial-manager-lupus-therapeutics-lupus-research-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Co-Executive Director, Development</t>
+  </si>
+  <si>
+    <t>Cook Inletkeeper</t>
+  </si>
+  <si>
+    <t>Homer, Alaska</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/363d0cb0f7224a03b62d7e7299ca6113-co-executive-director-development-cook-inletkeeper-homer</t>
+  </si>
+  <si>
+    <t>Communications &amp; Partnerships Manager</t>
+  </si>
+  <si>
+    <t>Our Family Coalition</t>
+  </si>
+  <si>
+    <t>OAKLAND, California</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fe676f21f624262821f747d0de0086b-communications-partnerships-manager-our-family-coalition-oakland</t>
+  </si>
+  <si>
+    <t>Communications and Marketing Specialist</t>
+  </si>
+  <si>
+    <t>Ballard Food Bank</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c50847be6f1943faa5437e36824ae84e-communications-and-marketing-specialist-ballard-food-bank-seattle</t>
+  </si>
+  <si>
+    <t>Community Partners Trainer (RN)</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec32bf91df7e416aa0cc5948cf1da83f-community-partners-trainer-rn-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Coordinator, Institutional Advancement</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 49350.00 - 55125.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c3d836ad481f48acb1162a2da93b8d02-coordinator-institutional-advancement-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Coordinator, Regional Office Palm Beach</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>West Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f58d3437e1e49ff87e3cefa6036b7ae-coordinator-regional-office-palm-beach-ajc-west-palm-beach</t>
+  </si>
+  <si>
+    <t>Criminal/Immigration Senior Staff or Managing Attorneys</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>USD 112492.23/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed6ed5474d4c45b384d215f22dc810c9-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41638d24186e4e969da44343c696bcd5-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Remote (Fresno, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d94ee3bb0a646a59306b131765cc4f4-criminalimmigration-senior-staff-or-managing-attorneys-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>Cybersecurity Engineer</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9661638397d14e339f1e35e1bb0cd1d6-cybersecurity-engineer-civilization-research-institute-asheville</t>
+  </si>
+  <si>
+    <t>Data Analyst, Fundraising</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/868125da91af40818a0f51e0e50ce32b-data-analyst-fundraising-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Visual AIDS</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Health Medicine, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/371166902b7f4823845d459a6d8bac75-development-director-visual-aids-new-york</t>
+  </si>
+  <si>
+    <t>Development Director - Posse Bay Area</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4515989c14794130ae76d4e3b475574f-development-director-posse-bay-area-the-posse-foundation-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Development Director - Posse Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60c8bd098dee4e2c87aa7de21b559c8a-development-director-posse-los-angeles-the-posse-foundation-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Engagement Manager</t>
+  </si>
+  <si>
+    <t>SAGE | Advocacy and Services for LGBT Elders, Inc.</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9af3043f257040568a1fa3ee78e49f4b-development-engagement-manager-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>PeaceJam Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Denver, Colorado)</t>
+  </si>
+  <si>
+    <t>USD 5000.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23359f3913194146bd191cdf78e0e7f8-development-manager-peacejam-foundation-denver</t>
+  </si>
+  <si>
+    <t>Pro Bono Institute</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fe27179fd284f8182bd15af1a916140-development-manager-pro-bono-institute-washington</t>
+  </si>
+  <si>
     <t>Director of Communications and Systems</t>
   </si>
   <si>
@@ -445,6 +964,105 @@
     <t>https://www.idealist.org/en/nonprofit-job/a451bce684ad41d181f9ff4a542e4e68-director-of-communications-and-systems-mid-hudson-energy-transition-kingston</t>
   </si>
   <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>HAVEN</t>
+  </si>
+  <si>
+    <t>Bozeman, Montana</t>
+  </si>
+  <si>
+    <t>USD 102371.00 - 109921.00/year</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0ce532f337f430cae16512d76dd811f-director-of-development-haven-bozeman</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>NAMI GLAC</t>
+  </si>
+  <si>
+    <t>Los Angeles County, California</t>
+  </si>
+  <si>
+    <t>Community Development, Mental Health, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23320ed3383346d185cae2e8c9e838b9-director-of-operations-nami-glac-los-angeles-county</t>
+  </si>
+  <si>
+    <t>Director of Programs and Prevention Education</t>
+  </si>
+  <si>
+    <t>Immigrant Social Services</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d83c7b16adb4b49980a8b83af210835-director-of-programs-and-prevention-education-immigrant-social-services-new-york</t>
+  </si>
+  <si>
+    <t>Education Manager, JA Innovation Center @ Lawrence High School</t>
+  </si>
+  <si>
+    <t>Junior Achievement of Greater Boston</t>
+  </si>
+  <si>
+    <t>Lawrence, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87c3cd913d7840b4bd2abd779043b1cb-education-manager-ja-innovation-center-lawrence-high-school-junior-achievement-of-greater-boston-lawrence</t>
+  </si>
+  <si>
+    <t>Educational Consultant – Remote (Commission-based)</t>
+  </si>
+  <si>
+    <t>Shiva's Tutorial</t>
+  </si>
+  <si>
+    <t>Remote (IN)</t>
+  </si>
+  <si>
+    <t>INR 0.00 - 0.00/year</t>
+  </si>
+  <si>
+    <t>Education, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d4dd172009d442d881c7bc690225338-educational-consultant-remote-commission-based-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Underground Storage Tanks and Technical Assistance Specialist</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Lowell, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38a05da6c4234c938fba9549fd13550f-environmental-analyst-underground-storage-tanks-and-technical-assistance-specialist-neiwpcc-lowell</t>
+  </si>
+  <si>
     <t>Event Specialist</t>
   </si>
   <si>
@@ -463,6 +1081,327 @@
     <t>https://www.idealist.org/en/nonprofit-job/976123ef402f417ab329b90a515b4b5d-event-specialist-international-ocd-foundation-boston</t>
   </si>
   <si>
+    <t>Little Elm Area Food Bank</t>
+  </si>
+  <si>
+    <t>Little Elm, Texas</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83590c21f36a4d6db3dd0c1f76fc13cc-executive-director-little-elm-area-food-bank-little-elm</t>
+  </si>
+  <si>
+    <t>EXECUTIVE FOR SPIRITUAL GROWTH AND FORMATION</t>
+  </si>
+  <si>
+    <t>United Women in Faith</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f4abafd17514fdda7af04b4ba51d1c0-executive-for-spiritual-growth-and-formation-united-women-in-faith-new-york</t>
+  </si>
+  <si>
+    <t>Finance and Operations Manager</t>
+  </si>
+  <si>
+    <t>SLMath</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f40dcd82f574b888b8cc43297b5e083-finance-and-operations-manager-slmath-berkeley</t>
+  </si>
+  <si>
+    <t>Finance and/or Operations Manager</t>
+  </si>
+  <si>
+    <t>Recovery Cafe San Jose</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af77dc24275c49788728c7de7b19413c-finance-andor-operations-manager-recovery-cafe-san-jose-san-jose</t>
+  </si>
+  <si>
+    <t>Finance Director</t>
+  </si>
+  <si>
+    <t>Democratic Socialists of America</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6f2777a0c40431c8e43090861ae5a6c-finance-director-democratic-socialists-of-america-new-york</t>
+  </si>
+  <si>
+    <t>Finance Manager - Resilient Strategies LLC</t>
+  </si>
+  <si>
+    <t>Resilient Strategies LLC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/040e66fce2e54b038d3b887244376b37-finance-manager-resilient-strategies-llc-resilient-strategies-llc-oakland</t>
+  </si>
+  <si>
+    <t>FSF job opportunity: Systems Integration Administrator</t>
+  </si>
+  <si>
+    <t>Free Software Foundation</t>
+  </si>
+  <si>
+    <t>USD 81369.60 - 81369.60/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/019087f91ab8412c934d46bc0f1bdb2b-fsf-job-opportunity-systems-integration-administrator-free-software-foundation-boston</t>
+  </si>
+  <si>
+    <t>Fundraising Database &amp; Operations Director (Raiser's Edge)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2453f5c88f5a49ea98698b1368ad7da2-fundraising-database-operations-director-raisers-edge-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Fundraising Systems &amp; Research Associate (Salesforce)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6ca44f2cebf24cf284a6a39228b5262b-fundraising-systems-research-associate-salesforce-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Grant Coordinator</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7a0b083054442748ee904f4a34860ad-grant-coordinator-florida-association-of-free-and-charitable-clinics-jacksonville</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53102309e3a0409cb541f01e19574791-graphic-designer-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Housing Assistant (Entry level)</t>
+  </si>
+  <si>
+    <t>We Stay/Nos Quedamos</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1206e3293591454cb7056f4135ba4b1f-housing-assistant-entry-level-we-staynos-quedamos-bronx</t>
+  </si>
+  <si>
+    <t>IMMIGRATION LAW ATTORNEY CWJC (Springfield)</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b20e0aee2c8747bba7bf00a5a1c6880c-immigration-law-attorney-cwjc-springfield-community-legal-aid-affiliate-springfield</t>
+  </si>
+  <si>
+    <t>Lead Canvasser, Civic Engagement</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3292f02e19574c8f91e2fee79c5433d7-lead-canvasser-civic-engagement-hispanic-federation-orlando</t>
+  </si>
+  <si>
+    <t>LEAD TEACHER BILINGUAL ENG-SPA - 2ND GRADE</t>
+  </si>
+  <si>
+    <t>Mundo Verde Bilingual Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 62222.00 - 92653.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d03bddb143541268aa6dd741ed554cf-lead-teacher-bilingual-eng-spa-2nd-grade-mundo-verde-bilingual-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>Lighting Supervisor</t>
+  </si>
+  <si>
+    <t>Signature Theatre</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b84b0c4b504541eeb9152330bf0ff2ef-lighting-supervisor-signature-theatre-arlington</t>
+  </si>
+  <si>
+    <t>Manager of Project Wishes</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Greater Bay Area</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10667a24c1834b1da572e09dedc921a7-manager-of-project-wishes-make-a-wish-greater-bay-area-oakland</t>
+  </si>
+  <si>
+    <t>Manager of Schoolwide Assessment, Data and Accountability</t>
+  </si>
+  <si>
+    <t>Bridges Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 82500.00 - 104500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c406c89ef950492183eeeaa82ceb8567-manager-of-schoolwide-assessment-data-and-accountability-bridges-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>Manager Of Youth Programs</t>
+  </si>
+  <si>
+    <t>Live Out Loud (New York based)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fca06db8cc36467581cd35401bc565c4-manager-of-youth-programs-live-out-loud-new-york-based-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Communications &amp; Marketing</t>
+  </si>
+  <si>
+    <t>National Society to Prevent Blindness d/b/a Prevent Blindness</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a77ff56243c243699f06a1a470fbea3d-manager-communications-marketing-national-society-to-prevent-blindness-dba-prevent-blindness-chicago</t>
+  </si>
+  <si>
+    <t>Manager, Contracts and Agreements</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f350f25e98624f99a2659b4ae09e6b44-manager-contracts-and-agreements-lupus-research-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Mobile Pantry Part-Time Commodities Associate</t>
+  </si>
+  <si>
+    <t>New York Common Pantry</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f486666b275a4e4bbd286960e02cc016-mobile-pantry-part-time-commodities-associate-new-york-common-pantry-bronx</t>
+  </si>
+  <si>
+    <t>Neighborhood 360 Program Manager</t>
+  </si>
+  <si>
+    <t>Myrtle Avenue Brooklyn Partnership</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91011c5d2cc24263bbd92399f6749c0e-neighborhood-360-program-manager-myrtle-avenue-brooklyn-partnership-kings-county</t>
+  </si>
+  <si>
     <t>Nonprofit Finance Manager</t>
   </si>
   <si>
@@ -476,6 +1415,570 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/consultant-job/5388f5cc13e24eee8351945ee5e94c0e-nonprofit-finance-manager-100-degrees-consulting-clarence-center</t>
+  </si>
+  <si>
+    <t>Office Coordinator</t>
+  </si>
+  <si>
+    <t>Madison Community Foundation</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3544598822734505a9dc4f1c4749989c-office-coordinator-madison-community-foundation-madison</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>Good Shepherd Volunteers</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5e682a29287407fa5d6c33aacff9cf3-operations-assistant-good-shepherd-volunteers-queens-county</t>
+  </si>
+  <si>
+    <t>Operations Director</t>
+  </si>
+  <si>
+    <t>American Association of University Professors</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4aa852c074a74a638503a8e196ea5a7a-operations-director-american-association-of-university-professors-washington</t>
+  </si>
+  <si>
+    <t>Outreach and Partnerships Senior Coordinator</t>
+  </si>
+  <si>
+    <t>UnLocal, Inc.</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdd195b16b3b4102a3ad2a775b3b405b-outreach-and-partnerships-senior-coordinator-unlocal-inc-new-york</t>
+  </si>
+  <si>
+    <t>Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Sunnyside Community Services, Inc.</t>
+  </si>
+  <si>
+    <t>Sunnyside, NY</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d3d3345dd114df8ac015725bb0b1f9d-outreach-coordinator-sunnyside-community-services-inc-sunnyside</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>The Resurrection Project</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/751a0d79fb8b4d9bb4464faa2c3c0a70-paralegal-the-resurrection-project-chicago</t>
+  </si>
+  <si>
+    <t>Part-Time Administrative Assistant for San Francisco Nonprofit</t>
+  </si>
+  <si>
+    <t>The Forgotten International</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Women, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d39bc079c3641eda81764266001239b-part-time-administrative-assistant-for-san-francisco-nonprofit-the-forgotten-international-san-francisco</t>
+  </si>
+  <si>
+    <t>Part-time Communications Associate - Jews of Color Initiative</t>
+  </si>
+  <si>
+    <t>Jews of Color Initiative</t>
+  </si>
+  <si>
+    <t>Communications Access, Media, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89a534296d7941fb9c2a9010bd159dab-part-time-communications-associate-jews-of-color-initiative-jews-of-color-initiative-berkeley</t>
+  </si>
+  <si>
+    <t>Pessoa Assessora de Captação de Recursos, Relacionamento e Governança</t>
+  </si>
+  <si>
+    <t>Instituto de Defesa do Direito de Defesa - Marcio Thomaz Bastos</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6296910642074dc5a05b468e33c4b287-pessoa-assessora-de-captacao-de-recursos-relacionamento-e-governanca-instituto-de-defesa-do-direito-de-defesa-marcio-thomaz-bastos-sao-paulo</t>
+  </si>
+  <si>
+    <t>Philanthropy Manager</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/498e8d6f79ac42ca80b48f34d34fe382-philanthropy-manager-third-way-washington</t>
+  </si>
+  <si>
+    <t>PR &amp; Communications Partner</t>
+  </si>
+  <si>
+    <t>SAADA</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/826acbbc82f1491989e829d4b5e9c76d-pr-communications-partner-saada-philadelphia</t>
+  </si>
+  <si>
+    <t>Procurement Analyst</t>
+  </si>
+  <si>
+    <t>City of Somerville</t>
+  </si>
+  <si>
+    <t>Somerville, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/586856ceebf84beeab54e3b71384a787-procurement-analyst-city-of-somerville-somerville</t>
+  </si>
+  <si>
+    <t>Program Associate, Faculty Institute</t>
+  </si>
+  <si>
+    <t>C&amp;S</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3af085ecf30442999a8a1fb0c25ec565-program-associate-faculty-institute-cs-princeton</t>
+  </si>
+  <si>
+    <t>Project Manager (Health Programs)</t>
+  </si>
+  <si>
+    <t>Alliance for a Healthier Generation</t>
+  </si>
+  <si>
+    <t>Remote (South Carolina)</t>
+  </si>
+  <si>
+    <t>USD 62800.00 - 94200.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bf2e6e2a94e42268192a73c81dcc39a-project-manager-health-programs-alliance-for-a-healthier-generation-portland</t>
+  </si>
+  <si>
+    <t>Promotor de Proyecto Especial en Migración - Tapachula Chiapas</t>
+  </si>
+  <si>
+    <t>World Vision México</t>
+  </si>
+  <si>
+    <t>Tapachula de Córdova y Ordóñez, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 11782.00 - 11782.00/month</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Children Youth, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd521f28c0094e58be2f4b50b8f0d43c-promotor-de-proyecto-especial-en-migracion-tapachula-chiapas-world-vision-mexico-tapachula-de-cordova-y-ordonez</t>
+  </si>
+  <si>
+    <t>Promotor de Proyecto Especial en Migración - Tijuana, B.C.</t>
+  </si>
+  <si>
+    <t>Tijuana, Baja California, MX</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d123c71e7b654323a0b640966ee5958b-promotor-de-proyecto-especial-en-migracion-tijuana-bc-world-vision-mexico-tijuana</t>
+  </si>
+  <si>
+    <t>PT Program Assistant, Outreach</t>
+  </si>
+  <si>
+    <t>Trinity Church NYC</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6eef04922dec47dea3b8e7328278f74b-pt-program-assistant-outreach-trinity-church-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Rental Coordinator</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist Church at Washington Crossing</t>
+  </si>
+  <si>
+    <t>Hopewell Township, New Jersey</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1c8d110c3ce47248700b053eab2cc24-rental-coordinator-unitarian-universalist-church-at-washington-crossing-hopewell-township</t>
+  </si>
+  <si>
+    <t>Resource Specialist / Systems Navigator</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/039193d8cf974d4e94907e97dd0adca0-resource-specialist-systems-navigator-recovery-cafe-san-jose-san-jose</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Institutional Advancement</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 60638.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/23305b48c73a49a290a6fed535274e1a-senior-coordinator-institutional-advancement-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Senior Director of Finance</t>
+  </si>
+  <si>
+    <t>Haymarket Center</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbf4ea5a0b2c4c148233096d48dfe813-senior-director-of-finance-haymarket-center-chicago</t>
+  </si>
+  <si>
+    <t>Senior Director of Marketing &amp; Communications</t>
+  </si>
+  <si>
+    <t>USD 136000.00 - 136000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32340d152b284f23a9ad9c5652ca8b21-senior-director-of-marketing-communications-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Grants &amp; Foundations Manager</t>
+  </si>
+  <si>
+    <t>Green America (formerly Co-op America)</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78f9570e6026413d9798ace618770f09-senior-grants-foundations-manager-green-america-formerly-co-op-america-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Scientific Program Operations</t>
+  </si>
+  <si>
+    <t>Lymphoma Research Foundation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34582515d36141d4a7cc5577597d854d-senior-manager-scientific-program-operations-lymphoma-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>SNAP Specialist, Russian Speaking</t>
+  </si>
+  <si>
+    <t>Metropolitan Council on Jewish Poverty</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d86e904537e4a6eb98a51f4ce290783-snap-specialist-russian-speaking-metropolitan-council-on-jewish-poverty-new-york</t>
+  </si>
+  <si>
+    <t>Social Media Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>Congressional Communities Inc.</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/098fbe9d7767400f9442c6ef59dcd319-social-media-manager-part-time-congressional-communities-inc-aliso-viejo</t>
+  </si>
+  <si>
+    <t>Special AE</t>
+  </si>
+  <si>
+    <t>The Museum of Modern Art</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84c53d4b28ae429ca6dd0c42245a7f24-special-ae-the-museum-of-modern-art-new-york</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c81cd6f33650429e99327781080ec290-staff-accountant-food-water-watch-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Society of Eastern Virginia</t>
+  </si>
+  <si>
+    <t>Hampton, Virginia</t>
+  </si>
+  <si>
+    <t>USD 72000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/807d666a6ec444c8b72281937817e445-staff-attorney-legal-aid-society-of-eastern-virginia-hampton</t>
+  </si>
+  <si>
+    <t>Norfolk, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76dbcbbe819a4ccb95bdd7ef61ab3639-staff-attorney-legal-aid-society-of-eastern-virginia-norfolk</t>
+  </si>
+  <si>
+    <t>Texas RioGrande Legal Aid, Inc. (TRLA)</t>
+  </si>
+  <si>
+    <t>Harlingen, Texas</t>
+  </si>
+  <si>
+    <t>USD 66929.00 - 91067.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3612228e43b1467eb2d745dd816d97ec-staff-attorney-texas-riogrande-legal-aid-inc-trla-harlingen</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 100532.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6feb6490fd5a447893bcb040edd261fd-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney – Housing and Disability Advocacy Program (HDAP)</t>
+  </si>
+  <si>
+    <t>LEGAL AID SOCIETY OF SAN BERNARDINO</t>
+  </si>
+  <si>
+    <t>San Bernadino, CA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ed9a0a9e66844610a3d3e95b2accba9c-staff-attorney-housing-and-disability-advocacy-program-hdap-legal-aid-society-of-san-bernardino-san-bernadino</t>
+  </si>
+  <si>
+    <t>Staff Attorney- San Joaquin Valley</t>
+  </si>
+  <si>
+    <t>USD 93509.70/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d79785126e34d8a9c876c67609a7b22-staff-attorney-san-joaquin-valley-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>Sunday Child-Care Aide at Unitarian Universalist Congregation of Greater Naples, Inc. (UUCGN)</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist Congregation of Greater Naples</t>
+  </si>
+  <si>
+    <t>Naples, Florida</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f99051bc21924ed3b0dcc80014d70f42-sunday-child-care-aide-at-unitarian-universalist-congregation-of-greater-naples-inc-uucgn-unitarian-universalist-congregation-of-greater-naples-naples</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ce27d95f45a47bdb598cc7dff8819b8-supervising-attorney-catholic-charities-archdiocese-of-ny-new-york</t>
+  </si>
+  <si>
+    <t>Supervisión de innovación de Trabajadoras Comunitarias de Salud (enfoque en Atención Clínica)</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 21000.00 - 21000.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27ac1d50da61406cb3cbc0392cac909f-supervision-de-innovacion-de-trabajadoras-comunitarias-de-salud-enfoque-en-atencion-clinica-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Temporary Food Drive Assistant</t>
+  </si>
+  <si>
+    <t>Alameda County Community Food Bank</t>
+  </si>
+  <si>
+    <t>USD 31.20 - 31.20/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19681332e49849ef865e94b08e975c9d-temporary-food-drive-assistant-alameda-county-community-food-bank-oakland</t>
+  </si>
+  <si>
+    <t>Temporary Law Graduate/Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 87994.00 - 93265.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68b25541de2e4430a37d0f8025c174c6-temporary-law-graduatestaff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Workers' Rights Program Director</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>USD 161197.00 - 176144.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e25850f9ef24b589ddb0ed954ea8cca-workers-rights-program-director-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Youth Program Facilitator (Ossining, Port Chester or Mt. Vernon)</t>
+  </si>
+  <si>
+    <t>Girls Inc. of Westchester County</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d15a8015bca4409d8d31aa6cd07df3a8-youth-program-facilitator-ossining-port-chester-or-mt-vernon-girls-inc-of-westchester-county-white-plains</t>
   </si>
 </sst>
 </file>
@@ -1487,7 +2990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1583,39 +3086,2408 @@
         <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
         <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F14" t="s">
         <v>153</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" t="s">
+        <v>217</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" t="s">
+        <v>223</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" t="s">
+        <v>228</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
+        <v>239</v>
+      </c>
+      <c r="F20" t="s">
+        <v>240</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" t="s">
+        <v>246</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" t="s">
+        <v>255</v>
+      </c>
+      <c r="D23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" t="s">
+        <v>260</v>
+      </c>
+      <c r="D24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" t="s">
+        <v>261</v>
+      </c>
+      <c r="F24" t="s">
+        <v>262</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C25" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" t="s">
+        <v>267</v>
+      </c>
+      <c r="F25" t="s">
+        <v>268</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" t="s">
+        <v>268</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" t="s">
+        <v>271</v>
+      </c>
+      <c r="D27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F27" t="s">
+        <v>268</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" t="s">
+        <v>275</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s">
+        <v>278</v>
+      </c>
+      <c r="C29" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" t="s">
+        <v>279</v>
+      </c>
+      <c r="F29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B30" t="s">
+        <v>282</v>
+      </c>
+      <c r="C30" t="s">
+        <v>283</v>
+      </c>
+      <c r="D30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" t="s">
+        <v>284</v>
+      </c>
+      <c r="F30" t="s">
+        <v>285</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" t="s">
+        <v>289</v>
+      </c>
+      <c r="F31" t="s">
+        <v>290</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s">
+        <v>288</v>
+      </c>
+      <c r="C32" t="s">
+        <v>293</v>
+      </c>
+      <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" t="s">
+        <v>289</v>
+      </c>
+      <c r="F32" t="s">
+        <v>290</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
+        <v>297</v>
+      </c>
+      <c r="F33" t="s">
+        <v>298</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B34" t="s">
+        <v>301</v>
+      </c>
+      <c r="C34" t="s">
+        <v>302</v>
+      </c>
+      <c r="D34" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" t="s">
+        <v>303</v>
+      </c>
+      <c r="F34" t="s">
+        <v>304</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" t="s">
+        <v>306</v>
+      </c>
+      <c r="C35" t="s">
+        <v>255</v>
+      </c>
+      <c r="D35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" t="s">
+        <v>307</v>
+      </c>
+      <c r="F35" t="s">
+        <v>308</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>310</v>
+      </c>
+      <c r="B36" t="s">
+        <v>311</v>
+      </c>
+      <c r="C36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
+        <v>313</v>
+      </c>
+      <c r="F36" t="s">
+        <v>314</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>316</v>
+      </c>
+      <c r="B37" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>319</v>
+      </c>
+      <c r="F37" t="s">
+        <v>320</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>322</v>
+      </c>
+      <c r="B38" t="s">
+        <v>323</v>
+      </c>
+      <c r="C38" t="s">
+        <v>324</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" t="s">
+        <v>325</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>327</v>
+      </c>
+      <c r="B39" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" t="s">
+        <v>165</v>
+      </c>
+      <c r="F39" t="s">
+        <v>329</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" t="s">
+        <v>333</v>
+      </c>
+      <c r="D40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" t="s">
+        <v>334</v>
+      </c>
+      <c r="F40" t="s">
+        <v>335</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>337</v>
+      </c>
+      <c r="B41" t="s">
+        <v>338</v>
+      </c>
+      <c r="C41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" t="s">
+        <v>340</v>
+      </c>
+      <c r="F41" t="s">
+        <v>341</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>343</v>
+      </c>
+      <c r="B42" t="s">
+        <v>344</v>
+      </c>
+      <c r="C42" t="s">
+        <v>345</v>
+      </c>
+      <c r="D42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" t="s">
+        <v>346</v>
+      </c>
+      <c r="F42" t="s">
+        <v>347</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>349</v>
+      </c>
+      <c r="B43" t="s">
+        <v>350</v>
+      </c>
+      <c r="C43" t="s">
+        <v>351</v>
+      </c>
+      <c r="D43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" t="s">
+        <v>352</v>
+      </c>
+      <c r="F43" t="s">
+        <v>353</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>355</v>
+      </c>
+      <c r="C44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" t="s">
+        <v>357</v>
+      </c>
+      <c r="F44" t="s">
+        <v>358</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B45" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" t="s">
+        <v>362</v>
+      </c>
+      <c r="F45" t="s">
+        <v>363</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>365</v>
+      </c>
+      <c r="B46" t="s">
+        <v>366</v>
+      </c>
+      <c r="C46" t="s">
+        <v>367</v>
+      </c>
+      <c r="D46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" t="s">
+        <v>368</v>
+      </c>
+      <c r="F46" t="s">
+        <v>194</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>370</v>
+      </c>
+      <c r="B47" t="s">
+        <v>371</v>
+      </c>
+      <c r="C47" t="s">
+        <v>372</v>
+      </c>
+      <c r="D47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" t="s">
+        <v>373</v>
+      </c>
+      <c r="F47" t="s">
+        <v>374</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>376</v>
+      </c>
+      <c r="B48" t="s">
+        <v>377</v>
+      </c>
+      <c r="C48" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" t="s">
+        <v>378</v>
+      </c>
+      <c r="F48" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>380</v>
+      </c>
+      <c r="B49" t="s">
+        <v>381</v>
+      </c>
+      <c r="C49" t="s">
+        <v>192</v>
+      </c>
+      <c r="D49" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F49" t="s">
+        <v>153</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>384</v>
+      </c>
+      <c r="B50" t="s">
+        <v>385</v>
+      </c>
+      <c r="C50" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" t="s">
+        <v>386</v>
+      </c>
+      <c r="F50" t="s">
+        <v>387</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>389</v>
+      </c>
+      <c r="B51" t="s">
+        <v>390</v>
+      </c>
+      <c r="C51" t="s">
+        <v>255</v>
+      </c>
+      <c r="D51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" t="s">
+        <v>391</v>
+      </c>
+      <c r="F51" t="s">
+        <v>392</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>394</v>
+      </c>
+      <c r="B52" t="s">
+        <v>390</v>
+      </c>
+      <c r="C52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D52" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" t="s">
+        <v>395</v>
+      </c>
+      <c r="F52" t="s">
+        <v>396</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>398</v>
+      </c>
+      <c r="B53" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" t="s">
+        <v>399</v>
+      </c>
+      <c r="F53" t="s">
+        <v>148</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>401</v>
+      </c>
+      <c r="B54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C54" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" t="s">
+        <v>402</v>
+      </c>
+      <c r="F54" t="s">
+        <v>403</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>405</v>
+      </c>
+      <c r="B55" t="s">
+        <v>406</v>
+      </c>
+      <c r="C55" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" t="s">
+        <v>146</v>
+      </c>
+      <c r="E55" t="s">
+        <v>407</v>
+      </c>
+      <c r="F55" t="s">
+        <v>408</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>410</v>
+      </c>
+      <c r="B56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" t="s">
+        <v>411</v>
+      </c>
+      <c r="D56" t="s">
+        <v>146</v>
+      </c>
+      <c r="E56" t="s">
+        <v>412</v>
+      </c>
+      <c r="F56" t="s">
+        <v>211</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>414</v>
+      </c>
+      <c r="B57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" t="s">
+        <v>203</v>
+      </c>
+      <c r="D57" t="s">
+        <v>204</v>
+      </c>
+      <c r="E57" t="s">
+        <v>415</v>
+      </c>
+      <c r="F57" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>417</v>
+      </c>
+      <c r="B58" t="s">
+        <v>418</v>
+      </c>
+      <c r="C58" t="s">
+        <v>255</v>
+      </c>
+      <c r="D58" t="s">
+        <v>146</v>
+      </c>
+      <c r="E58" t="s">
+        <v>419</v>
+      </c>
+      <c r="F58" t="s">
+        <v>420</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>422</v>
+      </c>
+      <c r="B59" t="s">
+        <v>423</v>
+      </c>
+      <c r="C59" t="s">
+        <v>424</v>
+      </c>
+      <c r="D59" t="s">
+        <v>146</v>
+      </c>
+      <c r="E59" t="s">
+        <v>425</v>
+      </c>
+      <c r="F59" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B60" t="s">
+        <v>428</v>
+      </c>
+      <c r="C60" t="s">
+        <v>429</v>
+      </c>
+      <c r="D60" t="s">
+        <v>146</v>
+      </c>
+      <c r="E60" t="s">
+        <v>430</v>
+      </c>
+      <c r="F60" t="s">
+        <v>431</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>433</v>
+      </c>
+      <c r="B61" t="s">
+        <v>434</v>
+      </c>
+      <c r="C61" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" t="s">
+        <v>435</v>
+      </c>
+      <c r="F61" t="s">
+        <v>436</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>438</v>
+      </c>
+      <c r="B62" t="s">
+        <v>439</v>
+      </c>
+      <c r="C62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D62" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" t="s">
+        <v>440</v>
+      </c>
+      <c r="F62" t="s">
+        <v>441</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>443</v>
+      </c>
+      <c r="B63" t="s">
+        <v>444</v>
+      </c>
+      <c r="C63" t="s">
+        <v>445</v>
+      </c>
+      <c r="D63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
+        <v>446</v>
+      </c>
+      <c r="F63" t="s">
+        <v>447</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>449</v>
+      </c>
+      <c r="B64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" t="s">
+        <v>192</v>
+      </c>
+      <c r="D64" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" t="s">
+        <v>402</v>
+      </c>
+      <c r="F64" t="s">
+        <v>228</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>451</v>
+      </c>
+      <c r="B65" t="s">
+        <v>452</v>
+      </c>
+      <c r="C65" t="s">
+        <v>453</v>
+      </c>
+      <c r="D65" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" t="s">
+        <v>454</v>
+      </c>
+      <c r="F65" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>456</v>
+      </c>
+      <c r="B66" t="s">
+        <v>457</v>
+      </c>
+      <c r="C66" t="s">
+        <v>458</v>
+      </c>
+      <c r="D66" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" t="s">
+        <v>459</v>
+      </c>
+      <c r="F66" t="s">
+        <v>460</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>462</v>
+      </c>
+      <c r="B67" t="s">
+        <v>463</v>
+      </c>
+      <c r="C67" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" t="s">
+        <v>464</v>
+      </c>
+      <c r="F67" t="s">
+        <v>465</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>467</v>
+      </c>
+      <c r="B68" t="s">
+        <v>468</v>
+      </c>
+      <c r="C68" t="s">
+        <v>469</v>
+      </c>
+      <c r="D68" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" t="s">
+        <v>147</v>
+      </c>
+      <c r="F68" t="s">
+        <v>403</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>471</v>
+      </c>
+      <c r="B69" t="s">
+        <v>472</v>
+      </c>
+      <c r="C69" t="s">
+        <v>473</v>
+      </c>
+      <c r="D69" t="s">
+        <v>133</v>
+      </c>
+      <c r="E69" t="s">
+        <v>474</v>
+      </c>
+      <c r="F69" t="s">
+        <v>475</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>477</v>
+      </c>
+      <c r="B70" t="s">
+        <v>478</v>
+      </c>
+      <c r="C70" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" t="s">
+        <v>146</v>
+      </c>
+      <c r="E70" t="s">
+        <v>479</v>
+      </c>
+      <c r="F70" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>481</v>
+      </c>
+      <c r="B71" t="s">
+        <v>482</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" t="s">
+        <v>483</v>
+      </c>
+      <c r="F71" t="s">
+        <v>484</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>486</v>
+      </c>
+      <c r="B72" t="s">
+        <v>487</v>
+      </c>
+      <c r="C72" t="s">
+        <v>488</v>
+      </c>
+      <c r="D72" t="s">
+        <v>146</v>
+      </c>
+      <c r="E72" t="s">
+        <v>261</v>
+      </c>
+      <c r="F72" t="s">
+        <v>489</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>491</v>
+      </c>
+      <c r="B73" t="s">
+        <v>492</v>
+      </c>
+      <c r="C73" t="s">
+        <v>445</v>
+      </c>
+      <c r="D73" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" t="s">
+        <v>493</v>
+      </c>
+      <c r="F73" t="s">
+        <v>494</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>496</v>
+      </c>
+      <c r="B74" t="s">
+        <v>497</v>
+      </c>
+      <c r="C74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" t="s">
+        <v>133</v>
+      </c>
+      <c r="E74" t="s">
+        <v>498</v>
+      </c>
+      <c r="F74" t="s">
+        <v>499</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>501</v>
+      </c>
+      <c r="B75" t="s">
+        <v>502</v>
+      </c>
+      <c r="C75" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" t="s">
+        <v>133</v>
+      </c>
+      <c r="E75" t="s">
+        <v>395</v>
+      </c>
+      <c r="F75" t="s">
+        <v>503</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>505</v>
+      </c>
+      <c r="B76" t="s">
+        <v>506</v>
+      </c>
+      <c r="C76" t="s">
+        <v>507</v>
+      </c>
+      <c r="D76" t="s">
+        <v>146</v>
+      </c>
+      <c r="E76" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" t="s">
+        <v>508</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>510</v>
+      </c>
+      <c r="B77" t="s">
+        <v>511</v>
+      </c>
+      <c r="C77" t="s">
+        <v>255</v>
+      </c>
+      <c r="D77" t="s">
+        <v>146</v>
+      </c>
+      <c r="E77" t="s">
+        <v>512</v>
+      </c>
+      <c r="F77" t="s">
+        <v>153</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>514</v>
+      </c>
+      <c r="B78" t="s">
+        <v>515</v>
+      </c>
+      <c r="C78" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" t="s">
+        <v>250</v>
+      </c>
+      <c r="E78" t="s">
+        <v>516</v>
+      </c>
+      <c r="F78" t="s">
+        <v>517</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>519</v>
+      </c>
+      <c r="B79" t="s">
+        <v>520</v>
+      </c>
+      <c r="C79" t="s">
+        <v>521</v>
+      </c>
+      <c r="D79" t="s">
+        <v>146</v>
+      </c>
+      <c r="E79" t="s">
+        <v>522</v>
+      </c>
+      <c r="F79" t="s">
+        <v>523</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>525</v>
+      </c>
+      <c r="B80" t="s">
+        <v>526</v>
+      </c>
+      <c r="C80" t="s">
+        <v>192</v>
+      </c>
+      <c r="D80" t="s">
+        <v>146</v>
+      </c>
+      <c r="E80" t="s">
+        <v>527</v>
+      </c>
+      <c r="F80" t="s">
+        <v>528</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>530</v>
+      </c>
+      <c r="B81" t="s">
+        <v>531</v>
+      </c>
+      <c r="C81" t="s">
+        <v>532</v>
+      </c>
+      <c r="D81" t="s">
+        <v>146</v>
+      </c>
+      <c r="E81" t="s">
+        <v>533</v>
+      </c>
+      <c r="F81" t="s">
+        <v>534</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>536</v>
+      </c>
+      <c r="B82" t="s">
+        <v>537</v>
+      </c>
+      <c r="C82" t="s">
+        <v>538</v>
+      </c>
+      <c r="D82" t="s">
+        <v>176</v>
+      </c>
+      <c r="E82" t="s">
+        <v>539</v>
+      </c>
+      <c r="F82" t="s">
+        <v>540</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>542</v>
+      </c>
+      <c r="B83" t="s">
+        <v>537</v>
+      </c>
+      <c r="C83" t="s">
+        <v>543</v>
+      </c>
+      <c r="D83" t="s">
+        <v>176</v>
+      </c>
+      <c r="E83" t="s">
+        <v>539</v>
+      </c>
+      <c r="F83" t="s">
+        <v>544</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>546</v>
+      </c>
+      <c r="B84" t="s">
+        <v>547</v>
+      </c>
+      <c r="C84" t="s">
+        <v>164</v>
+      </c>
+      <c r="D84" t="s">
+        <v>133</v>
+      </c>
+      <c r="E84" t="s">
+        <v>548</v>
+      </c>
+      <c r="F84" t="s">
+        <v>549</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>551</v>
+      </c>
+      <c r="B85" t="s">
+        <v>552</v>
+      </c>
+      <c r="C85" t="s">
+        <v>553</v>
+      </c>
+      <c r="D85" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85" t="s">
+        <v>153</v>
+      </c>
+      <c r="F85" t="s">
+        <v>554</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>556</v>
+      </c>
+      <c r="B86" t="s">
+        <v>371</v>
+      </c>
+      <c r="C86" t="s">
+        <v>372</v>
+      </c>
+      <c r="D86" t="s">
+        <v>133</v>
+      </c>
+      <c r="E86" t="s">
+        <v>557</v>
+      </c>
+      <c r="F86" t="s">
+        <v>374</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>559</v>
+      </c>
+      <c r="B87" t="s">
+        <v>254</v>
+      </c>
+      <c r="C87" t="s">
+        <v>255</v>
+      </c>
+      <c r="D87" t="s">
+        <v>146</v>
+      </c>
+      <c r="E87" t="s">
+        <v>560</v>
+      </c>
+      <c r="F87" t="s">
+        <v>153</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>562</v>
+      </c>
+      <c r="B88" t="s">
+        <v>563</v>
+      </c>
+      <c r="C88" t="s">
+        <v>445</v>
+      </c>
+      <c r="D88" t="s">
+        <v>146</v>
+      </c>
+      <c r="E88" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88" t="s">
+        <v>564</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>566</v>
+      </c>
+      <c r="B89" t="s">
+        <v>296</v>
+      </c>
+      <c r="C89" t="s">
+        <v>192</v>
+      </c>
+      <c r="D89" t="s">
+        <v>146</v>
+      </c>
+      <c r="E89" t="s">
+        <v>567</v>
+      </c>
+      <c r="F89" t="s">
+        <v>298</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>569</v>
+      </c>
+      <c r="B90" t="s">
+        <v>570</v>
+      </c>
+      <c r="C90" t="s">
+        <v>192</v>
+      </c>
+      <c r="D90" t="s">
+        <v>146</v>
+      </c>
+      <c r="E90" t="s">
+        <v>233</v>
+      </c>
+      <c r="F90" t="s">
+        <v>571</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>573</v>
+      </c>
+      <c r="B91" t="s">
+        <v>574</v>
+      </c>
+      <c r="C91" t="s">
+        <v>283</v>
+      </c>
+      <c r="D91" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" t="s">
+        <v>575</v>
+      </c>
+      <c r="F91" t="s">
+        <v>576</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>578</v>
+      </c>
+      <c r="B92" t="s">
+        <v>579</v>
+      </c>
+      <c r="C92" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" t="s">
+        <v>146</v>
+      </c>
+      <c r="E92" t="s">
+        <v>580</v>
+      </c>
+      <c r="F92" t="s">
+        <v>581</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>583</v>
+      </c>
+      <c r="B93" t="s">
+        <v>584</v>
+      </c>
+      <c r="C93" t="s">
+        <v>192</v>
+      </c>
+      <c r="D93" t="s">
+        <v>133</v>
+      </c>
+      <c r="E93" t="s">
+        <v>585</v>
+      </c>
+      <c r="F93" t="s">
+        <v>586</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>588</v>
+      </c>
+      <c r="B94" t="s">
+        <v>589</v>
+      </c>
+      <c r="C94" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" t="s">
+        <v>146</v>
+      </c>
+      <c r="E94" t="s">
+        <v>590</v>
+      </c>
+      <c r="F94" t="s">
+        <v>154</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>592</v>
+      </c>
+      <c r="B95" t="s">
+        <v>593</v>
+      </c>
+      <c r="C95" t="s">
+        <v>594</v>
+      </c>
+      <c r="D95" t="s">
+        <v>146</v>
+      </c>
+      <c r="E95" t="s">
+        <v>402</v>
+      </c>
+      <c r="F95" t="s">
+        <v>595</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>597</v>
+      </c>
+      <c r="B96" t="s">
+        <v>598</v>
+      </c>
+      <c r="C96" t="s">
+        <v>599</v>
+      </c>
+      <c r="D96" t="s">
+        <v>146</v>
+      </c>
+      <c r="E96" t="s">
+        <v>600</v>
+      </c>
+      <c r="F96" t="s">
+        <v>601</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>597</v>
+      </c>
+      <c r="B97" t="s">
+        <v>598</v>
+      </c>
+      <c r="C97" t="s">
+        <v>603</v>
+      </c>
+      <c r="D97" t="s">
+        <v>146</v>
+      </c>
+      <c r="E97" t="s">
+        <v>600</v>
+      </c>
+      <c r="F97" t="s">
+        <v>153</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>597</v>
+      </c>
+      <c r="B98" t="s">
+        <v>605</v>
+      </c>
+      <c r="C98" t="s">
+        <v>606</v>
+      </c>
+      <c r="D98" t="s">
+        <v>146</v>
+      </c>
+      <c r="E98" t="s">
+        <v>607</v>
+      </c>
+      <c r="F98" t="s">
+        <v>608</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>597</v>
+      </c>
+      <c r="B99" t="s">
+        <v>610</v>
+      </c>
+      <c r="C99" t="s">
+        <v>164</v>
+      </c>
+      <c r="D99" t="s">
+        <v>146</v>
+      </c>
+      <c r="E99" t="s">
+        <v>611</v>
+      </c>
+      <c r="F99" t="s">
+        <v>308</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>613</v>
+      </c>
+      <c r="B100" t="s">
+        <v>614</v>
+      </c>
+      <c r="C100" t="s">
+        <v>615</v>
+      </c>
+      <c r="D100" t="s">
+        <v>146</v>
+      </c>
+      <c r="E100" t="s">
+        <v>382</v>
+      </c>
+      <c r="F100" t="s">
+        <v>153</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>617</v>
+      </c>
+      <c r="B101" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" t="s">
+        <v>271</v>
+      </c>
+      <c r="D101" t="s">
+        <v>146</v>
+      </c>
+      <c r="E101" t="s">
+        <v>618</v>
+      </c>
+      <c r="F101" t="s">
+        <v>268</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>620</v>
+      </c>
+      <c r="B102" t="s">
+        <v>621</v>
+      </c>
+      <c r="C102" t="s">
+        <v>622</v>
+      </c>
+      <c r="D102" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" t="s">
+        <v>623</v>
+      </c>
+      <c r="F102" t="s">
+        <v>420</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>625</v>
+      </c>
+      <c r="B103" t="s">
+        <v>626</v>
+      </c>
+      <c r="C103" t="s">
+        <v>164</v>
+      </c>
+      <c r="D103" t="s">
+        <v>146</v>
+      </c>
+      <c r="E103" t="s">
+        <v>627</v>
+      </c>
+      <c r="F103" t="s">
+        <v>628</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>630</v>
+      </c>
+      <c r="B104" t="s">
+        <v>631</v>
+      </c>
+      <c r="C104" t="s">
+        <v>632</v>
+      </c>
+      <c r="D104" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" t="s">
+        <v>633</v>
+      </c>
+      <c r="F104" t="s">
+        <v>634</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>636</v>
+      </c>
+      <c r="B105" t="s">
+        <v>637</v>
+      </c>
+      <c r="C105" t="s">
+        <v>429</v>
+      </c>
+      <c r="D105" t="s">
+        <v>176</v>
+      </c>
+      <c r="E105" t="s">
+        <v>638</v>
+      </c>
+      <c r="F105" t="s">
+        <v>639</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>641</v>
+      </c>
+      <c r="B106" t="s">
+        <v>610</v>
+      </c>
+      <c r="C106" t="s">
+        <v>164</v>
+      </c>
+      <c r="D106" t="s">
+        <v>146</v>
+      </c>
+      <c r="E106" t="s">
+        <v>642</v>
+      </c>
+      <c r="F106" t="s">
+        <v>308</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>644</v>
+      </c>
+      <c r="B107" t="s">
+        <v>645</v>
+      </c>
+      <c r="C107" t="s">
+        <v>132</v>
+      </c>
+      <c r="D107" t="s">
+        <v>146</v>
+      </c>
+      <c r="E107" t="s">
+        <v>646</v>
+      </c>
+      <c r="F107" t="s">
+        <v>647</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>649</v>
+      </c>
+      <c r="B108" t="s">
+        <v>650</v>
+      </c>
+      <c r="C108" t="s">
+        <v>651</v>
+      </c>
+      <c r="D108" t="s">
+        <v>133</v>
+      </c>
+      <c r="E108" t="s">
+        <v>652</v>
+      </c>
+      <c r="F108" t="s">
+        <v>653</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -1625,6 +5497,109 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-27.xlsx
+++ b/docs/xlsx/jobs-2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="687">
   <si>
     <t>Title</t>
   </si>
@@ -406,6 +406,27 @@
     <t>https://www.conservationjobboard.com/job-listing-workers-compensation-specialist-remote-remote/4671046176</t>
   </si>
   <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Climate Interactive</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/chief-operating-officer-6/</t>
+  </si>
+  <si>
     <t>Academic Tutor (Part-Time)</t>
   </si>
   <si>
@@ -535,6 +556,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6cf21d409c0343fa88a37d3c3a3d5124-associatesenior-counsel-voting-rights-latinojustice-prldef-new-york</t>
   </si>
   <si>
+    <t>Bi Lingual Program Assistant</t>
+  </si>
+  <si>
+    <t>Girl Vow, Inc.</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29c87a3d21644afc8ff45507f2bc9e91-bi-lingual-program-assistant-girl-vow-inc-new-york</t>
+  </si>
+  <si>
     <t>Bilingual (English/Spanish) Immigration Program Specialist</t>
   </si>
   <si>
@@ -592,9 +628,6 @@
     <t>ILO Group</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -790,6 +823,12 @@
     <t>https://www.idealist.org/en/job/c3d836ad481f48acb1162a2da93b8d02-coordinator-institutional-advancement-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>Meridian International</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c3d836ad481f48acb1162a2da93b8d02-coordinator-institutional-advancement-meridian-international-washington</t>
+  </si>
+  <si>
     <t>Coordinator, Regional Office Palm Beach</t>
   </si>
   <si>
@@ -1282,6 +1321,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/4d03bddb143541268aa6dd741ed554cf-lead-teacher-bilingual-eng-spa-2nd-grade-mundo-verde-bilingual-public-charter-school-washington</t>
   </si>
   <si>
+    <t>Legal Director, Food and Nutrition Program</t>
+  </si>
+  <si>
+    <t>Campaign for Tobacco-Free Kids</t>
+  </si>
+  <si>
+    <t>Washington, Washington D.C</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6252b9e83dbf45029b6b977c76786a8c-legal-director-food-and-nutrition-program-campaign-for-tobacco-free-kids-washington</t>
+  </si>
+  <si>
     <t>Lighting Supervisor</t>
   </si>
   <si>
@@ -1573,6 +1624,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/826acbbc82f1491989e829d4b5e9c76d-pr-communications-partner-saada-philadelphia</t>
   </si>
   <si>
+    <t>President &amp; Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Independent Television Service</t>
+  </si>
+  <si>
+    <t>USD 275000.00 - 275000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3fd53e98aaf547b0ad0167798401bb6e-president-chief-executive-officer-independent-television-service-san-francisco</t>
+  </si>
+  <si>
     <t>Procurement Analyst</t>
   </si>
   <si>
@@ -1702,6 +1768,9 @@
     <t>https://www.idealist.org/en/job/23305b48c73a49a290a6fed535274e1a-senior-coordinator-institutional-advancement-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/job/23305b48c73a49a290a6fed535274e1a-senior-coordinator-institutional-advancement-meridian-international-washington</t>
+  </si>
+  <si>
     <t>Senior Director of Finance</t>
   </si>
   <si>
@@ -1780,6 +1849,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/098fbe9d7767400f9442c6ef59dcd319-social-media-manager-part-time-congressional-communities-inc-aliso-viejo</t>
   </si>
   <si>
+    <t>Soup Kitchen Team Lead</t>
+  </si>
+  <si>
+    <t>HALEY HOUSE INC</t>
+  </si>
+  <si>
+    <t>USD 16.10 - 17.50/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bd58871d4004dbe9346ffc33bf124cb-soup-kitchen-team-lead-haley-house-inc-boston</t>
+  </si>
+  <si>
     <t>Special AE</t>
   </si>
   <si>
@@ -1867,6 +1951,12 @@
     <t>https://www.idealist.org/en/job/ed9a0a9e66844610a3d3e95b2accba9c-staff-attorney-housing-and-disability-advocacy-program-hdap-legal-aid-society-of-san-bernardino-san-bernadino</t>
   </si>
   <si>
+    <t>Staff Attorney – Housing or Family (Hybrid)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d9295995217648e192973c5e1a138c93-staff-attorney-housing-or-family-hybrid-legal-aid-society-of-san-bernardino-san-bernadino</t>
+  </si>
+  <si>
     <t>Staff Attorney- San Joaquin Valley</t>
   </si>
   <si>
@@ -1948,6 +2038,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/68b25541de2e4430a37d0f8025c174c6-temporary-law-graduatestaff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Testing Coordinator</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/050229eca04d46a899a8f8b6ea6f3300-testing-coordinator-bridges-public-charter-school-washington</t>
+  </si>
+  <si>
     <t>Workers' Rights Program Director</t>
   </si>
   <si>
@@ -1973,9 +2072,6 @@
   </si>
   <si>
     <t>USD 20.00 - 30.00/hour</t>
-  </si>
-  <si>
-    <t>Children Youth, Women</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d15a8015bca4409d8d31aa6cd07df3a8-youth-program-facilitator-ossining-port-chester-or-mt-vernon-girls-inc-of-westchester-county-white-plains</t>
@@ -2942,7 +3038,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2981,8 +3077,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2990,7 +3112,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3031,531 +3153,531 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F7" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F12" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F17" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E18" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F18" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B19" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C19" t="s">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F20" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F21" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E23" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F24" t="s">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3563,91 +3685,91 @@
         <v>264</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C25" t="s">
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
         <v>267</v>
       </c>
       <c r="F25" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F26" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3658,1206 +3780,1206 @@
         <v>278</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C30" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>284</v>
+        <v>160</v>
       </c>
       <c r="F30" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F31" t="s">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F32" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
         <v>301</v>
       </c>
       <c r="C34" t="s">
+        <v>306</v>
+      </c>
+      <c r="D34" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" t="s">
         <v>302</v>
       </c>
-      <c r="D34" t="s">
-        <v>250</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>303</v>
       </c>
-      <c r="F34" t="s">
-        <v>304</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C35" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E36" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F36" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C37" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F37" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E38" t="s">
-        <v>165</v>
+        <v>326</v>
       </c>
       <c r="F38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>331</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>332</v>
       </c>
       <c r="F39" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C40" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>334</v>
+        <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C41" t="s">
-        <v>339</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>340</v>
+        <v>172</v>
       </c>
       <c r="F41" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C42" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E43" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E44" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F44" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E45" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F45" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>365</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C46" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E46" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F46" t="s">
-        <v>194</v>
+        <v>371</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D47" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E47" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F47" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>380</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F48" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E49" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F49" t="s">
-        <v>153</v>
+        <v>387</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E50" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F50" t="s">
-        <v>387</v>
+        <v>160</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E51" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F51" t="s">
-        <v>392</v>
+        <v>160</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C52" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="D52" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="E52" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F52" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>403</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F53" t="s">
-        <v>148</v>
+        <v>405</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s">
-        <v>278</v>
+        <v>403</v>
       </c>
       <c r="C54" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F54" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B55" t="s">
-        <v>406</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F55" t="s">
-        <v>408</v>
+        <v>155</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>291</v>
       </c>
       <c r="C56" t="s">
-        <v>411</v>
+        <v>171</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E56" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F56" t="s">
-        <v>211</v>
+        <v>416</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>419</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D57" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>421</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s">
-        <v>418</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="F58" t="s">
-        <v>420</v>
+        <v>222</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s">
-        <v>423</v>
+        <v>213</v>
       </c>
       <c r="C59" t="s">
-        <v>424</v>
+        <v>214</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="E59" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F59" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C60" t="s">
-        <v>429</v>
+        <v>266</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F60" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>437</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E61" t="s">
-        <v>435</v>
+        <v>160</v>
       </c>
       <c r="F61" t="s">
-        <v>436</v>
+        <v>160</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C62" t="s">
-        <v>164</v>
+        <v>441</v>
       </c>
       <c r="D62" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F62" t="s">
-        <v>441</v>
+        <v>161</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C63" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E63" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>451</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E64" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="F64" t="s">
-        <v>228</v>
+        <v>453</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C65" t="s">
-        <v>453</v>
+        <v>171</v>
       </c>
       <c r="D65" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E65" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F65" t="s">
-        <v>153</v>
+        <v>458</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D66" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F66" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B67" t="s">
-        <v>463</v>
+        <v>237</v>
       </c>
       <c r="C67" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E67" t="s">
-        <v>464</v>
+        <v>415</v>
       </c>
       <c r="F67" t="s">
-        <v>465</v>
+        <v>239</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C68" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>147</v>
+        <v>471</v>
       </c>
       <c r="F68" t="s">
-        <v>403</v>
+        <v>160</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B69" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C69" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E69" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F69" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E70" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F70" t="s">
-        <v>194</v>
+        <v>482</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B71" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C71" t="s">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E71" t="s">
-        <v>483</v>
+        <v>154</v>
       </c>
       <c r="F71" t="s">
-        <v>484</v>
+        <v>416</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B72" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C72" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
-        <v>261</v>
+        <v>491</v>
       </c>
       <c r="F72" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C73" t="s">
-        <v>445</v>
+        <v>266</v>
       </c>
       <c r="D73" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E73" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F73" t="s">
-        <v>494</v>
+        <v>205</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C74" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F74" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B75" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C75" t="s">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E75" t="s">
-        <v>395</v>
+        <v>274</v>
       </c>
       <c r="F75" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C76" t="s">
-        <v>507</v>
+        <v>462</v>
       </c>
       <c r="D76" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E76" t="s">
-        <v>153</v>
+        <v>510</v>
       </c>
       <c r="F76" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="D77" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E77" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F77" t="s">
-        <v>153</v>
+        <v>516</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C78" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="E78" t="s">
-        <v>516</v>
+        <v>408</v>
       </c>
       <c r="F78" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C79" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D79" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E79" t="s">
-        <v>522</v>
+        <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C80" t="s">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E80" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F80" t="s">
-        <v>528</v>
+        <v>160</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B81" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C81" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E81" t="s">
         <v>533</v>
@@ -4877,292 +4999,292 @@
         <v>537</v>
       </c>
       <c r="C82" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" t="s">
+        <v>153</v>
+      </c>
+      <c r="E82" t="s">
         <v>538</v>
       </c>
-      <c r="D82" t="s">
-        <v>176</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>539</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H82" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>541</v>
+      </c>
+      <c r="B83" t="s">
         <v>542</v>
-      </c>
-      <c r="B83" t="s">
-        <v>537</v>
       </c>
       <c r="C83" t="s">
         <v>543</v>
       </c>
       <c r="D83" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F83" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C84" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E84" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F84" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B85" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C85" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D85" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>555</v>
       </c>
       <c r="F85" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B86" t="s">
-        <v>371</v>
+        <v>559</v>
       </c>
       <c r="C86" t="s">
-        <v>372</v>
+        <v>560</v>
       </c>
       <c r="D86" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="E86" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F86" t="s">
-        <v>374</v>
+        <v>562</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>564</v>
+      </c>
+      <c r="B87" t="s">
         <v>559</v>
       </c>
-      <c r="B87" t="s">
-        <v>254</v>
-      </c>
       <c r="C87" t="s">
-        <v>255</v>
+        <v>565</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E87" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F87" t="s">
-        <v>153</v>
+        <v>566</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B88" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C88" t="s">
-        <v>445</v>
+        <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E88" t="s">
-        <v>222</v>
+        <v>570</v>
       </c>
       <c r="F88" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B89" t="s">
-        <v>296</v>
+        <v>574</v>
       </c>
       <c r="C89" t="s">
-        <v>192</v>
+        <v>575</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="E89" t="s">
-        <v>567</v>
+        <v>160</v>
       </c>
       <c r="F89" t="s">
-        <v>298</v>
+        <v>576</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s">
-        <v>570</v>
+        <v>384</v>
       </c>
       <c r="C90" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>579</v>
       </c>
       <c r="F90" t="s">
-        <v>571</v>
+        <v>387</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B91" t="s">
-        <v>574</v>
+        <v>265</v>
       </c>
       <c r="C91" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E91" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="F91" t="s">
-        <v>576</v>
+        <v>160</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s">
-        <v>579</v>
+        <v>269</v>
       </c>
       <c r="C92" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E92" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F92" t="s">
-        <v>581</v>
+        <v>160</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B93" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C93" t="s">
-        <v>192</v>
+        <v>462</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E93" t="s">
-        <v>585</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s">
-        <v>589</v>
+        <v>309</v>
       </c>
       <c r="C94" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E94" t="s">
         <v>590</v>
       </c>
       <c r="F94" t="s">
-        <v>154</v>
+        <v>311</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>591</v>
@@ -5176,180 +5298,180 @@
         <v>593</v>
       </c>
       <c r="C95" t="s">
+        <v>132</v>
+      </c>
+      <c r="D95" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" t="s">
+        <v>244</v>
+      </c>
+      <c r="F95" t="s">
         <v>594</v>
       </c>
-      <c r="D95" t="s">
-        <v>146</v>
-      </c>
-      <c r="E95" t="s">
-        <v>402</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="H95" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>596</v>
+      </c>
+      <c r="B96" t="s">
         <v>597</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>296</v>
+      </c>
+      <c r="D96" t="s">
+        <v>153</v>
+      </c>
+      <c r="E96" t="s">
         <v>598</v>
       </c>
-      <c r="C96" t="s">
+      <c r="F96" t="s">
         <v>599</v>
       </c>
-      <c r="D96" t="s">
-        <v>146</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="H96" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="F96" t="s">
-        <v>601</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C97" t="s">
+        <v>171</v>
+      </c>
+      <c r="D97" t="s">
+        <v>153</v>
+      </c>
+      <c r="E97" t="s">
         <v>603</v>
       </c>
-      <c r="D97" t="s">
-        <v>146</v>
-      </c>
-      <c r="E97" t="s">
-        <v>600</v>
-      </c>
       <c r="F97" t="s">
-        <v>153</v>
+        <v>604</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C98" t="s">
-        <v>606</v>
+        <v>132</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E98" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F98" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B99" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C99" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="D99" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E99" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F99" t="s">
-        <v>308</v>
+        <v>614</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B100" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C100" t="s">
-        <v>615</v>
+        <v>171</v>
       </c>
       <c r="D100" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E100" t="s">
-        <v>382</v>
+        <v>618</v>
       </c>
       <c r="F100" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B101" t="s">
-        <v>265</v>
+        <v>621</v>
       </c>
       <c r="C101" t="s">
-        <v>271</v>
+        <v>622</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E101" t="s">
-        <v>618</v>
+        <v>415</v>
       </c>
       <c r="F101" t="s">
-        <v>268</v>
+        <v>623</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B102" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C102" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D102" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="E102" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="F102" t="s">
-        <v>420</v>
+        <v>629</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -5360,62 +5482,62 @@
         <v>626</v>
       </c>
       <c r="C103" t="s">
-        <v>164</v>
+        <v>631</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E103" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F103" t="s">
-        <v>628</v>
+        <v>160</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C104" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D104" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="E104" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F104" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B105" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C105" t="s">
-        <v>429</v>
+        <v>171</v>
       </c>
       <c r="D105" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="E105" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F105" t="s">
-        <v>639</v>
+        <v>321</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>640</v>
@@ -5426,68 +5548,252 @@
         <v>641</v>
       </c>
       <c r="B106" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="C106" t="s">
-        <v>164</v>
+        <v>643</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E106" t="s">
-        <v>642</v>
+        <v>395</v>
       </c>
       <c r="F106" t="s">
-        <v>308</v>
+        <v>160</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B107" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C107" t="s">
-        <v>132</v>
+        <v>643</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E107" t="s">
+        <v>160</v>
+      </c>
+      <c r="F107" t="s">
+        <v>160</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="F107" t="s">
-        <v>647</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>647</v>
+      </c>
+      <c r="B108" t="s">
+        <v>278</v>
+      </c>
+      <c r="C108" t="s">
+        <v>284</v>
+      </c>
+      <c r="D108" t="s">
+        <v>153</v>
+      </c>
+      <c r="E108" t="s">
+        <v>648</v>
+      </c>
+      <c r="F108" t="s">
+        <v>281</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B108" t="s">
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>650</v>
       </c>
-      <c r="C108" t="s">
+      <c r="B109" t="s">
         <v>651</v>
       </c>
-      <c r="D108" t="s">
-        <v>133</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="C109" t="s">
         <v>652</v>
       </c>
-      <c r="F108" t="s">
+      <c r="D109" t="s">
+        <v>261</v>
+      </c>
+      <c r="E109" t="s">
         <v>653</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="F109" t="s">
+        <v>433</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>654</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>655</v>
+      </c>
+      <c r="B110" t="s">
+        <v>656</v>
+      </c>
+      <c r="C110" t="s">
+        <v>171</v>
+      </c>
+      <c r="D110" t="s">
+        <v>153</v>
+      </c>
+      <c r="E110" t="s">
+        <v>657</v>
+      </c>
+      <c r="F110" t="s">
+        <v>658</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>660</v>
+      </c>
+      <c r="B111" t="s">
+        <v>661</v>
+      </c>
+      <c r="C111" t="s">
+        <v>662</v>
+      </c>
+      <c r="D111" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" t="s">
+        <v>663</v>
+      </c>
+      <c r="F111" t="s">
+        <v>664</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>666</v>
+      </c>
+      <c r="B112" t="s">
+        <v>667</v>
+      </c>
+      <c r="C112" t="s">
+        <v>446</v>
+      </c>
+      <c r="D112" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" t="s">
+        <v>668</v>
+      </c>
+      <c r="F112" t="s">
+        <v>669</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>671</v>
+      </c>
+      <c r="B113" t="s">
+        <v>638</v>
+      </c>
+      <c r="C113" t="s">
+        <v>171</v>
+      </c>
+      <c r="D113" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" t="s">
+        <v>672</v>
+      </c>
+      <c r="F113" t="s">
+        <v>321</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>674</v>
+      </c>
+      <c r="B114" t="s">
+        <v>451</v>
+      </c>
+      <c r="C114" t="s">
+        <v>125</v>
+      </c>
+      <c r="D114" t="s">
+        <v>140</v>
+      </c>
+      <c r="E114" t="s">
+        <v>675</v>
+      </c>
+      <c r="F114" t="s">
+        <v>160</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>677</v>
+      </c>
+      <c r="B115" t="s">
+        <v>678</v>
+      </c>
+      <c r="C115" t="s">
+        <v>139</v>
+      </c>
+      <c r="D115" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" t="s">
+        <v>679</v>
+      </c>
+      <c r="F115" t="s">
+        <v>680</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>682</v>
+      </c>
+      <c r="B116" t="s">
+        <v>683</v>
+      </c>
+      <c r="C116" t="s">
+        <v>684</v>
+      </c>
+      <c r="D116" t="s">
+        <v>140</v>
+      </c>
+      <c r="E116" t="s">
+        <v>685</v>
+      </c>
+      <c r="F116" t="s">
+        <v>183</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -5600,6 +5906,14 @@
     <hyperlink ref="H106" r:id="rId105"/>
     <hyperlink ref="H107" r:id="rId106"/>
     <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
